--- a/VT_AI_1.0_SUP.xlsx
+++ b/VT_AI_1.0_SUP.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79989682-2BA0-41F9-8B07-26B2C6D590A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F6F1D7-E154-4B8C-87FC-441F73B7B6F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-33840" yWindow="3075" windowWidth="28800" windowHeight="17265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Processes_and_Commodities" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="104">
   <si>
     <t>~FI_Comm</t>
   </si>
@@ -352,6 +352,9 @@
   </si>
   <si>
     <t>\I: *Region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEST 1 </t>
   </si>
 </sst>
 </file>
@@ -1782,6 +1785,11 @@
         <v>29</v>
       </c>
     </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>103</v>
+      </c>
+    </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.25">
       <c r="H30" s="5"/>
     </row>
